--- a/stories/arbres/ATOM-REL.AMI.001-09.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gaëtane est au square. Papa est au banc. Gaëtane a un cerceau. Le cerceau est bleu. Bertrand est là aussi. Gaëtane veut jouer. Papa dit : tu peux inviter. Inviter, c'est demander. Gaëtane dit : tu veux jouer ? Bertrand secoue la tête. Bertrand dit : non. Gaëtane a le ventre serré. Papa s'approche. Papa dit : on peut accepter un non. Accepter un non, c'est possible. Gaëtane dit : d'accord. Elle joue avec papa. Le cerceau roule. Bertrand joue avec un seau. Gaëtane n'insiste pas. Papa dit : merci. Tu as su inviter. Tu as su accepter un non.</t>
+          <t>Gaëtane est au square. Papa est au banc. Gaëtane a un cerceau. Le cerceau est bleu. Bertrand est là aussi. Gaëtane veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer ? Bertrand secoue la tête. Non. Gaëtane a le ventre serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Elle joue avec papa. Le cerceau roule. Bertrand joue avec un seau. Gaëtane n'insiste pas. Merci. Tu as su inviter. Tu as su accepter un non.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,20 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Gaëtane est au square. Papa est au banc. Gaëtane a un cerceau. Le cerceau est bleu. Bertrand est là aussi. Gaëtane veut jouer.
+papa|Tu peux inviter. Inviter, c'est demander.
+enfant-f|Tu veux jouer ?
+narrateur|Bertrand secoue la tête.
+copain|Non.
+narrateur|Gaëtane a le ventre serré. Papa s'approche.
+papa|On peut accepter un non. Accepter un non, c'est possible.
+enfant-f|D'accord. Elle joue avec papa.
+narrateur|Le cerceau roule. Bertrand joue avec un seau. Gaëtane n'insiste pas.
+papa|Merci. Tu as su inviter. Tu as su accepter un non.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Bertrand dit non. Que fait Gaëtane ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1668,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Gaëtane a su inviter. Bertrand a dit non. Gaëtane a pu accepter un non. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1835,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Gaëtane range le cerceau. Papa lui tend la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2002,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2042,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-09.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-09.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1319,6 +1324,7 @@
 papa|Merci. Tu as su inviter. Tu as su accepter un non.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1508,7 @@
           <t>narrateur|Bertrand dit non. Que fait Gaëtane ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1680,7 @@
           <t>narrateur|Gaëtane a su inviter. Bertrand a dit non. Gaëtane a pu accepter un non. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1840,6 +1848,7 @@
           <t>narrateur|Gaëtane range le cerceau. Papa lui tend la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2007,6 +2016,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2049,6 +2059,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2250,6 +2274,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.AMI.001-09.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gaëtane invite Bertrand</t>
+          <t>Le cerceau bleu de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina invite Raphaël avec son cerceau bleu. Raphaël dit non. Nina accepte et roule le cerceau avec papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gaëtane est au square. Papa est au banc. Gaëtane a un cerceau. Le cerceau est bleu. Bertrand est là aussi. Gaëtane veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer ? Bertrand secoue la tête. Non. Gaëtane a le ventre serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Elle joue avec papa. Le cerceau roule. Bertrand joue avec un seau. Gaëtane n'insiste pas. Merci. Tu as su inviter. Tu as su accepter un non.</t>
+          <t>Une flaque montre un nuage blanc. Le nuage est tout petit. Un cerceau bleu attend. Il est contre le banc. Ça sent l'herbe coupée. Un moineau saute près de l'eau. Nina, tu vois le nuage ? Oui, papa. Il est dans l'eau. Oui. Il est tout petit. En ce moment, Nina s'approche. Elle touche le cerceau. Il est lisse et froid. Il est bleu. Oui. C'est ton cerceau. Raphaël est là aussi. Il a un seau. Le seau est vert. Tu peux inviter. Inviter, c'est demander. Inviter, c'est demander. Tu veux jouer ? Raphaël secoue la tête. Non. Nina a le ventre serré. Le cerceau reste dans ses mains. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. On accepte un non. D'accord. Nina reste avec papa. Elle joue avec papa. Le cerceau roule. Il fait un petit bruit. Tu roules bien. Il est bleu. Oui. Tout bleu. Raphaël joue avec le seau. Le seau tape l'herbe. Nina accepte le non. Merci. Tu as su inviter. Tu as su accepter un non. Il a dit non. Un non, c'est possible. On roule encore ? Oui, papa. Le moineau saute encore. La flaque brille. Tu as fini avec le cerceau ? Oui. Bravo. Tu as fait du bon travail. Nina pose le cerceau. Le nuage n'est plus dans l'eau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,19 +1324,72 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Gaëtane est au square. Papa est au banc. Gaëtane a un cerceau. Le cerceau est bleu. Bertrand est là aussi. Gaëtane veut jouer.
-papa|Tu peux inviter. Inviter, c'est demander.
+          <t>narrateur|Une flaque montre un nuage blanc.
+narrateur|Le nuage est tout petit.
+narrateur|Un cerceau bleu attend.
+narrateur|Il est contre le banc.
+narrateur|Ça sent l'herbe coupée.
+narrateur|Un moineau saute près de l'eau.
+papa|Nina, tu vois le nuage ?
+enfant-f|Oui, papa.
+enfant-f|Il est dans l'eau.
+papa|Oui.
+papa|Il est tout petit.
+narrateur|En ce moment, Nina s'approche.
+narrateur|Elle touche le cerceau.
+narrateur|Il est lisse et froid.
+enfant-f|Il est bleu.
+papa|Oui.
+papa|C'est ton cerceau.
+narrateur|Raphaël est là aussi.
+narrateur|Il a un seau.
+narrateur|Le seau est vert.
+papa|Tu peux inviter.
+papa|Inviter, c'est demander.
+papa|Inviter, c'est demander.
 enfant-f|Tu veux jouer ?
-narrateur|Bertrand secoue la tête.
+narrateur|Raphaël secoue la tête.
 copain|Non.
-narrateur|Gaëtane a le ventre serré. Papa s'approche.
-papa|On peut accepter un non. Accepter un non, c'est possible.
-enfant-f|D'accord. Elle joue avec papa.
-narrateur|Le cerceau roule. Bertrand joue avec un seau. Gaëtane n'insiste pas.
-papa|Merci. Tu as su inviter. Tu as su accepter un non.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Nina a le ventre serré.
+narrateur|Le cerceau reste dans ses mains.
+narrateur|Papa s'approche.
+papa|On peut accepter un non.
+papa|Accepter un non, c'est possible.
+papa|On accepte un non.
+enfant-f|D'accord.
+narrateur|Nina reste avec papa.
+narrateur|Elle joue avec papa.
+narrateur|Le cerceau roule.
+narrateur|Il fait un petit bruit.
+papa|Tu roules bien.
+enfant-f|Il est bleu.
+papa|Oui.
+papa|Tout bleu.
+narrateur|Raphaël joue avec le seau.
+narrateur|Le seau tape l'herbe.
+narrateur|Nina accepte le non.
+papa|Merci.
+papa|Tu as su inviter.
+papa|Tu as su accepter un non.
+enfant-f|Il a dit non.
+papa|Un non, c'est possible.
+papa|On roule encore ?
+enfant-f|Oui, papa.
+narrateur|Le moineau saute encore.
+narrateur|La flaque brille.
+papa|Tu as fini avec le cerceau ?
+enfant-f|Oui.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Nina pose le cerceau.
+narrateur|Le nuage n'est plus dans l'eau.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1349,7 +1414,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Bertrand dit non. Que fait Gaëtane ?</t>
+          <t>Raphaël dit non. Que fait Nina ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1505,10 +1570,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Bertrand dit non. Que fait Gaëtane ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Raphaël dit non.
+narrateur|Que fait Nina ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,7 +1598,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gaëtane a su inviter. Bertrand a dit non. Gaëtane a pu accepter un non. Papa est là.</t>
+          <t>Nina a demandé. C'est inviter. Raphaël a dit non. Nina a accepté le non. Tu as su inviter. Tu as su accepter un non. Bravo, Nina. D'accord. Oui. Un non, c'est possible. Le cerceau bleu est au sol. Le seau vert est dans l'herbe. Tu as fini de jouer ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1677,10 +1742,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Gaëtane a su inviter. Bertrand a dit non. Gaëtane a pu accepter un non. Papa est là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina a demandé.
+narrateur|C'est inviter.
+narrateur|Raphaël a dit non.
+narrateur|Nina a accepté le non.
+papa|Tu as su inviter.
+papa|Tu as su accepter un non.
+papa|Bravo, Nina.
+enfant-f|D'accord.
+papa|Oui.
+papa|Un non, c'est possible.
+narrateur|Le cerceau bleu est au sol.
+narrateur|Le seau vert est dans l'herbe.
+papa|Tu as fini de jouer ?
+enfant-f|Oui, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1705,7 +1782,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Gaëtane range le cerceau. Papa lui tend la main.</t>
+          <t>Nina range le cerceau. Il est lisse et froid. Je tiens le sac. Il est bleu. Oui. On le met dans le sac. Tu prends ma main ? Oui. Ils quittent le square. Le moineau n'est plus là.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1845,10 +1922,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Gaëtane range le cerceau. Papa lui tend la main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nina range le cerceau.
+narrateur|Il est lisse et froid.
+papa|Je tiens le sac.
+enfant-f|Il est bleu.
+papa|Oui.
+papa|On le met dans le sac.
+papa|Tu prends ma main ?
+enfant-f|Oui.
+narrateur|Ils quittent le square.
+narrateur|Le moineau n'est plus là.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1873,7 +1958,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a invité. Elle a accepté un non. Le cerceau est dans le sac. Bravo, Nina. On rentre ? Oui. On rentre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2013,10 +2098,16 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Nina a invité.
+narrateur|Elle a accepté un non.
+narrateur|Le cerceau est dans le sac.
+papa|Bravo, Nina.
+enfant-f|On rentre ?
+papa|Oui.
+papa|On rentre.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2035,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2073,6 +2164,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-09.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-09.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une flaque montre un nuage blanc. Le nuage est tout petit. Un cerceau bleu attend. Il est contre le banc. Ça sent l'herbe coupée. Un moineau saute près de l'eau. Nina, tu vois le nuage ? Oui, papa. Il est dans l'eau. Oui. Il est tout petit. En ce moment, Nina s'approche. Elle touche le cerceau. Il est lisse et froid. Il est bleu. Oui. C'est ton cerceau. Raphaël est là aussi. Il a un seau. Le seau est vert. Tu peux inviter. Inviter, c'est demander. Inviter, c'est demander. Tu veux jouer ? Raphaël secoue la tête. Non. Nina a le ventre serré. Le cerceau reste dans ses mains. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. On accepte un non. D'accord. Nina reste avec papa. Elle joue avec papa. Le cerceau roule. Il fait un petit bruit. Tu roules bien. Il est bleu. Oui. Tout bleu. Raphaël joue avec le seau. Le seau tape l'herbe. Nina accepte le non. Merci. Tu as su inviter. Tu as su accepter un non. Il a dit non. Un non, c'est possible. On roule encore ? Oui, papa. Le moineau saute encore. La flaque brille. Tu as fini avec le cerceau ? Oui. Bravo. Tu as fait du bon travail. Nina pose le cerceau. Le nuage n'est plus dans l'eau.</t>
+          <t>Une flaque montre un nuage blanc. Le nuage est tout petit. Un cerceau bleu attend. Il est contre le banc. Ça sent l'herbe coupée. Un moineau saute près de l'eau. Nina, tu vois le nuage ? Oui, papa. Il est dans l'eau. Oui. Il est tout petit. En ce moment, Nina s'approche. Elle touche le cerceau. Il est lisse et froid. Il est bleu. Oui. C'est ton cerceau. Raphaël est là aussi. Il a un seau. Le seau est vert. Tu peux inviter. Inviter, c'est demander. Inviter, c'est demander. Tu veux jouer ? Raphaël secoue la tête. Non. Nina a le ventre serré. Le cerceau reste dans ses mains. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. On accepte un non. D'accord. Nina reste avec papa. Elle joue avec papa. Le cerceau roule. Il fait un petit bruit. Tu roules bien. Il est bleu. Oui. Tout bleu. Raphaël joue avec le seau. Le seau tape l'herbe. Nina accepte le non. Merci. Tu as su inviter. Tu as su accepter un non. Il a dit non. Un non, c'est possible. On roule encore ? Oui, papa. Le moineau saute encore. La flaque brille. Tu as fini avec le cerceau ? Oui. Bravo. Nina pose le cerceau. Le nuage n'est plus dans l'eau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Gaëtane est au square. Papa est au banc. Gaëtane a un cerceau. Le cerceau est bleu. Bertrand est là aussi. Gaëtane veut jouer. Papa dit : tu peux &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;. Inviter, c'est demander. Gaëtane dit : tu veux jouer ? Bertrand secoue la tête. Bertrand dit : non. Gaëtane a le ventre serré. Papa s'approche. Papa dit : on peut accepter un non. Accepter un non, c'est possible. Gaëtane dit : d'accord. Elle joue avec papa. Le cerceau roule. Bertrand joue avec un seau. Gaëtane n'insiste pas. Papa dit : merci. Tu as su inviter. Tu as su accepter un non.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une flaque montre un nuage blanc. Le nuage est tout petit. Un cerceau bleu attend. Il est contre le banc. Ça sent l'herbe coupée. Un moineau saute près de l'eau. Nina, tu vois le nuage ? Oui, papa. Il est dans l'eau. Oui. Il est tout petit. En ce moment, Nina s'approche. Elle touche le cerceau. Il est lisse et froid. Il est bleu. Oui. C'est ton cerceau. Raphaël est là aussi. Il a un seau. Le seau est vert. Tu peux inviter. Inviter, c'est demander. Inviter, c'est demander. Tu veux jouer ? Raphaël secoue la tête. Non. Nina a le ventre serré. Le cerceau reste dans ses mains. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. On accepte un non. D'accord. Nina reste avec papa. Elle joue avec papa. Le cerceau roule. Il fait un petit bruit. Tu roules bien. Il est bleu. Oui. Tout bleu. Raphaël joue avec le seau. Le seau tape l'herbe. Nina accepte le non. Merci. Tu as su inviter. Tu as su accepter un non. Il a dit non. Un non, c'est possible. On roule encore ? Oui, papa. Le moineau saute encore. La flaque brille. Tu as fini avec le cerceau ? Oui. Bravo. Nina pose le cerceau. Le nuage n'est plus dans l'eau.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1380,7 +1380,6 @@
 papa|Tu as fini avec le cerceau ?
 enfant-f|Oui.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Nina pose le cerceau.
 narrateur|Le nuage n'est plus dans l'eau.</t>
         </is>
@@ -1419,7 +1418,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Bertrand dit non. Que fait Gaëtane ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël dit non. Que fait Nina ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1603,7 +1602,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Gaëtane a su &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;. Bertrand a dit non. Gaëtane a pu accepter un non. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a demandé. C'est inviter. Raphaël a dit non. Nina a accepté le non. Tu as su inviter. Tu as su accepter un non. Bravo, Nina. D'accord. Oui. Un non, c'est possible. Le cerceau bleu est au sol. Le seau vert est dans l'herbe. Tu as fini de jouer ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1787,7 +1786,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Gaëtane range le cerceau. Papa lui tend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina range le cerceau. Il est lisse et froid. Je tiens le sac. Il est bleu. Oui. On le met dans le sac. Tu prends ma main ? Oui. Ils quittent le square. Le moineau n'est plus là.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1958,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nina a invité. Elle a accepté un non. Le cerceau est dans le sac. Bravo, Nina. On rentre ? Oui. On rentre. L'histoire est finie.</t>
+          <t>Nina a invité. Elle a accepté un non. Le cerceau est dans le sac. Bravo, Nina. On rentre ? Oui. On rentre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a invité. Elle a accepté un non. Le cerceau est dans le sac. Bravo, Nina. On rentre ? Oui. On rentre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2104,8 +2103,7 @@
 papa|Bravo, Nina.
 enfant-f|On rentre ?
 papa|Oui.
-papa|On rentre.
-narrateur|L'histoire est finie.</t>
+papa|On rentre.</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2171,6 +2169,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-09.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-09.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gaëtane, Bertrand, papa</t>
+          <t>Nina, Raphaël, papa</t>
         </is>
       </c>
     </row>
